--- a/hardware/Bill of Materials-111.xlsx
+++ b/hardware/Bill of Materials-111.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavel\Desktop\STM32_projects\MicroOhmMeter\Altium\111\Project Outputs for 111\Reports\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\STM32CubeIDE\STM32_projects\MicroOhmMeter\Altium\111\Project Outputs for 111\Reports\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D5A0396-2E0C-436C-A93A-18ADD49CF2B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EC4BD5D2-A36E-437E-9B0F-72AA0C4E9A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F8E3B11F-F397-4BBC-9A70-355A629F6AEE}"/>
+    <workbookView xWindow="-14370" yWindow="-7770" windowWidth="11370" windowHeight="19965" xr2:uid="{8157E205-682A-486D-AC85-C2CF5345A56B}"/>
   </bookViews>
   <sheets>
     <sheet name="Bill of Materials-111" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="171">
   <si>
     <t>Comment</t>
   </si>
@@ -66,7 +66,7 @@
     <t>C0603 22uF X8R 30ppm/°C 5.00% 10 V, C0603 1uF X8R 30ppm/°C 5.00% 50 V, C0603 100pF X8R 30ppm/°C 5.00% 50 V, C0603 100uF X8R 30ppm/°C 5.00% 10 V</t>
   </si>
   <si>
-    <t>C1, C3, C4, C5, C6, C7, C10, C11, C12, C13, C14, C21, C22, C23, C24</t>
+    <t>C1, C3, C4, C5, C6, C7, C10, C11, C12, C13, C14, C21, C22, C24, C25, C26</t>
   </si>
   <si>
     <t>FP-C0603C-CF-MFG</t>
@@ -171,6 +171,21 @@
     <t>D3, D5</t>
   </si>
   <si>
+    <t>BAT54C,215</t>
+  </si>
+  <si>
+    <t>DIODE ARRAY SCHOTTKY 30V SOT23</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>FP-SOT23-MFG</t>
+  </si>
+  <si>
+    <t>CMP-14398-000007-1</t>
+  </si>
+  <si>
     <t>B2B-XH-A(LF)(SN)</t>
   </si>
   <si>
@@ -252,6 +267,21 @@
     <t>CMP-32901-000143-1</t>
   </si>
   <si>
+    <t>BSS138</t>
+  </si>
+  <si>
+    <t>MOSFET N-CH 50V 220MA SOT-23</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>FP-318-08-IPC_B</t>
+  </si>
+  <si>
+    <t>CMP-07173-000101-1</t>
+  </si>
+  <si>
     <t>5 kOhms</t>
   </si>
   <si>
@@ -267,19 +297,22 @@
     <t>RK73H1JTTD1153F</t>
   </si>
   <si>
-    <t>115 kOhms</t>
+    <t>820 kOhms</t>
+  </si>
+  <si>
+    <t>RES 820K OHM 1% 1/10W 0603</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>15 kOhms</t>
-  </si>
-  <si>
-    <t>RES 15K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>R3</t>
+    <t>100 kOhms</t>
+  </si>
+  <si>
+    <t>RES 100K OHM 1% 1/10W 0603, RES 100 KOHM 1% 1/10W 0603, RES 10 KOHM 1% 1/10W 0603, RES 115K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R3, R14, R19, R24, R27</t>
   </si>
   <si>
     <t>1 kOhms</t>
@@ -351,15 +384,6 @@
     <t>R13</t>
   </si>
   <si>
-    <t>100 kOhms</t>
-  </si>
-  <si>
-    <t>RES 100 KOHM 1% 1/10W 0603, RES 10 KOHM 1% 1/10W 0603, RES 115K OHM 1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>R14, R19, R24, R27</t>
-  </si>
-  <si>
     <t>10 k</t>
   </si>
   <si>
@@ -402,6 +426,12 @@
     <t>RES_ERJU03J3R0V</t>
   </si>
   <si>
+    <t>RES 2K OHM 1% 1/10W 0603</t>
+  </si>
+  <si>
+    <t>R31, R32</t>
+  </si>
+  <si>
     <t>430152070826</t>
   </si>
   <si>
@@ -508,21 +538,6 @@
   </si>
   <si>
     <t>CMP-0758-00084-2</t>
-  </si>
-  <si>
-    <t>LTC2954</t>
-  </si>
-  <si>
-    <t>Pushbutton On / Off  Controller with µP Interrupt, 8-pin SOT23 (TS8-8), -40 to 85 degC, Pb-Free, Mini Tape and Reel</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>LT-TS8-8-TSOT-23_V</t>
-  </si>
-  <si>
-    <t>CMP-0482-01351-1</t>
   </si>
   <si>
     <t>ABM3BAIG-8.000MHZ-1Z-T</t>
@@ -914,8 +929,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{839CAC4D-815A-4F32-832A-7B864AE73408}">
-  <dimension ref="A1:F45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5C9C1C4-66BB-4A86-B312-0E0E6BC61948}">
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="6" width="19.7109375" customWidth="1"/>
@@ -958,7 +973,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="1">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1175,47 +1190,47 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F13" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="F14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="F15" s="1">
         <v>1</v>
@@ -1223,19 +1238,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>56</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="F16" s="1">
         <v>1</v>
@@ -1306,16 +1321,16 @@
         <v>75</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F20" s="1">
         <v>1</v>
@@ -1323,19 +1338,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F21" s="1">
         <v>1</v>
@@ -1343,79 +1358,79 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F22" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="F23" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F24" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F25" s="1">
         <v>3</v>
@@ -1423,59 +1438,59 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="F26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>101</v>
+        <v>6</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="F28" s="1">
         <v>1</v>
@@ -1483,79 +1498,79 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="F29" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>73</v>
+        <v>109</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="F30" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F32" s="1">
         <v>1</v>
@@ -1563,19 +1578,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F33" s="1">
         <v>1</v>
@@ -1583,19 +1598,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F34" s="1">
         <v>1</v>
@@ -1603,79 +1618,79 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>119</v>
+        <v>83</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="F35" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="F36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>127</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>124</v>
+        <v>84</v>
       </c>
       <c r="F37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="F38" s="1">
         <v>1</v>
@@ -1683,19 +1698,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="F39" s="1">
         <v>1</v>
@@ -1703,19 +1718,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="F40" s="1">
         <v>1</v>
@@ -1772,10 +1787,10 @@
         <v>154</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F43" s="1">
         <v>1</v>
@@ -1783,19 +1798,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F44" s="1">
         <v>1</v>
@@ -1803,21 +1818,41 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>165</v>
       </c>
       <c r="F45" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F46" s="1">
         <v>1</v>
       </c>
     </row>
